--- a/artfynd/A 43774-2026 artfynd.xlsx
+++ b/artfynd/A 43774-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,57 +905,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89120599</v>
+        <v>137435989</v>
       </c>
       <c r="B4" t="n">
-        <v>4781</v>
+        <v>79532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Förrådet, Upl</t>
+          <t>Söder om Gårdskärskustens naturreservat Billerud, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>642746</v>
+        <v>642688</v>
       </c>
       <c r="R4" t="n">
-        <v>6725949</v>
+        <v>6726011</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,12 +970,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-11-08</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-11-08</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,34 +994,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Thomas Stibe</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Thomas Stibe</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89120599</t>
+          <t>https://artportalen.se/Sighting/137435989</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67980360</v>
+        <v>89120599</v>
       </c>
       <c r="B5" t="n">
-        <v>97977</v>
+        <v>4781</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,39 +1028,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221944</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Förrådet, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>642650</v>
+        <v>642746</v>
       </c>
       <c r="R5" t="n">
-        <v>6725864</v>
+        <v>6725949</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,12 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-03-04</t>
+          <t>2020-11-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-03-04</t>
+          <t>2020-11-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,24 +1105,253 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/89120599</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>67980360</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Förrådet, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>642650</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6725864</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2017-03-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2017-03-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/67980360</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137435986</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101646</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Söder om Gårdskärskustens naturreservat Billerud, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>642500</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6725813</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Thomas Stibe</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Thomas Stibe</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435986</t>
         </is>
       </c>
     </row>
@@ -1128,6 +1361,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43774-2026 artfynd.xlsx
+++ b/artfynd/A 43774-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>137435989</v>
       </c>
       <c r="B4" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137435986</v>
       </c>
       <c r="B7" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43774-2026 artfynd.xlsx
+++ b/artfynd/A 43774-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>137435989</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137435986</v>
       </c>
       <c r="B7" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43774-2026 artfynd.xlsx
+++ b/artfynd/A 43774-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>137435989</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137435986</v>
       </c>
       <c r="B7" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
